--- a/source-docs/[source-docs-current-master] WWE_2K26_Liga_System_LY2_Opening_W46_abgeschlossen.xlsx
+++ b/source-docs/[source-docs-current-master] WWE_2K26_Liga_System_LY2_Opening_W46_abgeschlossen.xlsx
@@ -21134,7 +21134,7 @@
         <v>58</v>
       </c>
       <c r="J2" t="str">
-        <v>Champion + Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Champion + Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="3">
@@ -21166,7 +21166,7 @@
         <v>46</v>
       </c>
       <c r="J3" t="str">
-        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="4">
@@ -21198,7 +21198,7 @@
         <v>45</v>
       </c>
       <c r="J4" t="str">
-        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="5">
@@ -21230,7 +21230,7 @@
         <v>42</v>
       </c>
       <c r="J5" t="str">
-        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Elite Cup · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="6">
@@ -21262,7 +21262,7 @@
         <v>33</v>
       </c>
       <c r="J6" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="7">
@@ -21294,7 +21294,7 @@
         <v>30</v>
       </c>
       <c r="J7" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="8">
@@ -21326,7 +21326,7 @@
         <v>27</v>
       </c>
       <c r="J8" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="9">
@@ -21358,7 +21358,7 @@
         <v>21</v>
       </c>
       <c r="J9" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="10">
@@ -21390,7 +21390,7 @@
         <v>21</v>
       </c>
       <c r="J10" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="11">
@@ -21422,7 +21422,7 @@
         <v>18</v>
       </c>
       <c r="J11" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="12">
@@ -21454,7 +21454,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="str">
-        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="13">
@@ -21486,7 +21486,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="14">
@@ -21518,7 +21518,7 @@
         <v>52</v>
       </c>
       <c r="J14" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="15">
@@ -21550,7 +21550,7 @@
         <v>51</v>
       </c>
       <c r="J15" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="16">
@@ -21582,7 +21582,7 @@
         <v>48</v>
       </c>
       <c r="J16" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="17">
@@ -21614,7 +21614,7 @@
         <v>42</v>
       </c>
       <c r="J17" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="18">
@@ -21646,7 +21646,7 @@
         <v>34</v>
       </c>
       <c r="J18" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="19">
@@ -21678,7 +21678,7 @@
         <v>31</v>
       </c>
       <c r="J19" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="20">
@@ -21710,7 +21710,7 @@
         <v>30</v>
       </c>
       <c r="J20" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="21">
@@ -21742,7 +21742,7 @@
         <v>24</v>
       </c>
       <c r="J21" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="22">
@@ -21774,7 +21774,7 @@
         <v>19</v>
       </c>
       <c r="J22" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="23">
@@ -21806,7 +21806,7 @@
         <v>15</v>
       </c>
       <c r="J23" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="24">
@@ -21838,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="str">
-        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="25">
@@ -21870,7 +21870,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="str">
-        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="26">
@@ -21902,7 +21902,7 @@
         <v>51</v>
       </c>
       <c r="J26" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="27">
@@ -21934,7 +21934,7 @@
         <v>42</v>
       </c>
       <c r="J27" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="28">
@@ -21966,7 +21966,7 @@
         <v>39</v>
       </c>
       <c r="J28" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="29">
@@ -21998,7 +21998,7 @@
         <v>33</v>
       </c>
       <c r="J29" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="30">
@@ -22030,7 +22030,7 @@
         <v>30</v>
       </c>
       <c r="J30" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="31">
@@ -22062,7 +22062,7 @@
         <v>30</v>
       </c>
       <c r="J31" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="32">
@@ -22094,7 +22094,7 @@
         <v>24</v>
       </c>
       <c r="J32" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="33">
@@ -22126,7 +22126,7 @@
         <v>21</v>
       </c>
       <c r="J33" t="str">
-        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Sicher · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="34">
@@ -22158,7 +22158,7 @@
         <v>18</v>
       </c>
       <c r="J34" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="35">
@@ -22190,7 +22190,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="str">
-        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="36">
@@ -22222,7 +22222,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="str">
-        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach unten · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="37">
@@ -22254,7 +22254,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="str">
-        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Direkter Abstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="38">
@@ -22286,7 +22286,7 @@
         <v>53</v>
       </c>
       <c r="J38" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="39">
@@ -22318,7 +22318,7 @@
         <v>46</v>
       </c>
       <c r="J39" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="40">
@@ -22350,7 +22350,7 @@
         <v>45</v>
       </c>
       <c r="J40" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="41">
@@ -22382,7 +22382,7 @@
         <v>42</v>
       </c>
       <c r="J41" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="42">
@@ -22414,7 +22414,7 @@
         <v>27</v>
       </c>
       <c r="J42" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="43">
@@ -22446,7 +22446,7 @@
         <v>25</v>
       </c>
       <c r="J43" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="44">
@@ -22478,7 +22478,7 @@
         <v>24</v>
       </c>
       <c r="J44" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="45">
@@ -22510,7 +22510,7 @@
         <v>24</v>
       </c>
       <c r="J45" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="46">
@@ -22542,7 +22542,7 @@
         <v>21</v>
       </c>
       <c r="J46" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="47">
@@ -22574,7 +22574,7 @@
         <v>9</v>
       </c>
       <c r="J47" t="str">
-        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Bleibt in Regional · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="48">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Champion + direkter Aufstieg · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
     <row r="49">
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="str">
-        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
+        <v>Relegation nach oben · active split reset · active split reset · active split reset · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset · current composition · active split reset</v>
       </c>
     </row>
   </sheetData>
@@ -22650,7 +22650,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -23842,9 +23842,44 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35">
+        <v>46</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-06-22T14:02:11.532Z</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026-06-21T22:45:42.918Z</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>18</v>
+      </c>
+      <c r="F35" t="str">
+        <v>weekly-close-package-v1-week-46</v>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <v>[source-docs-current-master] WWE_2K26_Liga_System_LY2_Opening_W46_abgeschlossen.xlsx</v>
+      </c>
+      <c r="I35" t="str">
+        <v>updated workbook</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23944,7 +23979,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="3">
@@ -23991,7 +24026,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="4">
@@ -24038,7 +24073,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="5">
@@ -24085,7 +24120,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="6">
@@ -24132,7 +24167,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="7">
@@ -24179,7 +24214,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="8">
@@ -24226,7 +24261,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="9">
@@ -24273,7 +24308,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="10">
@@ -24320,7 +24355,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="11">
@@ -24367,7 +24402,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="12">
@@ -24414,7 +24449,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="13">
@@ -24461,7 +24496,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="14">
@@ -24508,7 +24543,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="15">
@@ -24555,7 +24590,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="16">
@@ -24602,7 +24637,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="17">
@@ -24649,7 +24684,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="18">
@@ -24696,7 +24731,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="19">
@@ -24743,7 +24778,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="20">
@@ -24790,7 +24825,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="21">
@@ -24837,7 +24872,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="22">
@@ -24884,7 +24919,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="23">
@@ -24931,7 +24966,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="24">
@@ -24978,7 +25013,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="25">
@@ -25025,7 +25060,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="26">
@@ -25072,7 +25107,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="27">
@@ -25119,7 +25154,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="28">
@@ -25166,7 +25201,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="29">
@@ -25213,7 +25248,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="30">
@@ -25260,7 +25295,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="31">
@@ -25307,7 +25342,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="32">
@@ -25354,7 +25389,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="33">
@@ -25401,7 +25436,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="34">
@@ -25448,7 +25483,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="35">
@@ -25495,7 +25530,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="36">
@@ -25542,7 +25577,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="37">
@@ -25589,7 +25624,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="38">
@@ -25636,7 +25671,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="39">
@@ -25683,7 +25718,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="40">
@@ -25730,7 +25765,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="41">
@@ -25777,7 +25812,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="42">
@@ -25824,7 +25859,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="43">
@@ -25871,7 +25906,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="44">
@@ -25918,7 +25953,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="45">
@@ -25965,7 +26000,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="46">
@@ -26012,7 +26047,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="47">
@@ -26059,7 +26094,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="48">
@@ -26106,7 +26141,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="49">
@@ -26153,7 +26188,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="50">
@@ -26200,7 +26235,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="51">
@@ -26247,7 +26282,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="52">
@@ -26294,7 +26329,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="53">
@@ -26341,7 +26376,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="54">
@@ -26388,7 +26423,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="55">
@@ -26435,7 +26470,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="56">
@@ -26482,7 +26517,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="57">
@@ -26529,7 +26564,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="58">
@@ -26576,7 +26611,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="59">
@@ -26623,7 +26658,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="60">
@@ -26670,7 +26705,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="61">
@@ -26717,7 +26752,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="62">
@@ -26764,7 +26799,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="63">
@@ -26811,7 +26846,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="64">
@@ -26858,7 +26893,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="65">
@@ -26905,7 +26940,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="66">
@@ -26952,7 +26987,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="67">
@@ -26999,7 +27034,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="68">
@@ -27046,7 +27081,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="69">
@@ -27093,7 +27128,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="70">
@@ -27140,7 +27175,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="71">
@@ -27187,7 +27222,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="72">
@@ -27234,7 +27269,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="73">
@@ -27281,7 +27316,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="74">
@@ -27328,7 +27363,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="75">
@@ -27375,7 +27410,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="76">
@@ -27422,7 +27457,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="77">
@@ -27469,7 +27504,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="78">
@@ -27516,7 +27551,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="79">
@@ -27563,7 +27598,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="80">
@@ -27610,7 +27645,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="81">
@@ -27657,7 +27692,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="82">
@@ -27704,7 +27739,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="83">
@@ -27751,7 +27786,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="84">
@@ -27798,7 +27833,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="85">
@@ -27845,7 +27880,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="86">
@@ -27892,7 +27927,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="87">
@@ -27939,7 +27974,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="88">
@@ -27986,7 +28021,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="89">
@@ -28033,7 +28068,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="90">
@@ -28080,7 +28115,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="91">
@@ -28127,7 +28162,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="92">
@@ -28174,7 +28209,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="93">
@@ -28221,7 +28256,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="94">
@@ -28268,7 +28303,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="95">
@@ -28315,7 +28350,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="96">
@@ -28362,7 +28397,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="97">
@@ -28409,7 +28444,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="98">
@@ -28456,7 +28491,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="99">
@@ -28503,7 +28538,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="100">
@@ -28550,7 +28585,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="101">
@@ -28597,7 +28632,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="102">
@@ -28644,7 +28679,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="103">
@@ -28691,7 +28726,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="104">
@@ -28738,7 +28773,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="105">
@@ -28785,7 +28820,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="106">
@@ -28832,7 +28867,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="107">
@@ -28879,7 +28914,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="108">
@@ -28926,7 +28961,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="109">
@@ -28973,7 +29008,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="110">
@@ -29020,7 +29055,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="111">
@@ -29067,7 +29102,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="112">
@@ -29114,7 +29149,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="113">
@@ -29161,7 +29196,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="114">
@@ -29208,7 +29243,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="115">
@@ -29255,7 +29290,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="116">
@@ -29302,7 +29337,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="117">
@@ -29349,7 +29384,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="118">
@@ -29396,7 +29431,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="119">
@@ -29443,7 +29478,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="120">
@@ -29490,7 +29525,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="121">
@@ -29537,7 +29572,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="122">
@@ -29584,7 +29619,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="123">
@@ -29631,7 +29666,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="124">
@@ -29678,7 +29713,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="125">
@@ -29725,7 +29760,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="126">
@@ -29772,7 +29807,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="127">
@@ -29819,7 +29854,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="128">
@@ -29866,7 +29901,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="129">
@@ -29913,7 +29948,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="130">
@@ -29960,7 +29995,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="131">
@@ -30007,7 +30042,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="132">
@@ -30054,7 +30089,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="133">
@@ -30101,7 +30136,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="134">
@@ -30148,7 +30183,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="135">
@@ -30195,7 +30230,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="136">
@@ -30242,7 +30277,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="137">
@@ -30289,7 +30324,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="138">
@@ -30336,7 +30371,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="139">
@@ -30383,7 +30418,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="140">
@@ -30430,7 +30465,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="141">
@@ -30477,7 +30512,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="142">
@@ -30524,7 +30559,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="143">
@@ -30571,7 +30606,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="144">
@@ -30618,7 +30653,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="145">
@@ -30665,7 +30700,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="146">
@@ -30712,7 +30747,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="147">
@@ -30759,7 +30794,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="148">
@@ -30806,7 +30841,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="149">
@@ -30853,7 +30888,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="150">
@@ -30900,7 +30935,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="151">
@@ -30947,7 +30982,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="152">
@@ -30994,7 +31029,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="153">
@@ -31041,7 +31076,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="154">
@@ -31088,7 +31123,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="155">
@@ -31135,7 +31170,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="156">
@@ -31182,7 +31217,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="157">
@@ -31229,7 +31264,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="158">
@@ -31276,7 +31311,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="159">
@@ -31323,7 +31358,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="160">
@@ -31370,7 +31405,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="161">
@@ -31417,7 +31452,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="162">
@@ -31464,7 +31499,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="163">
@@ -31511,7 +31546,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="164">
@@ -31558,7 +31593,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="165">
@@ -31605,7 +31640,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="166">
@@ -31652,7 +31687,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="167">
@@ -31699,7 +31734,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="168">
@@ -31746,7 +31781,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="169">
@@ -31793,7 +31828,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="170">
@@ -31840,7 +31875,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="171">
@@ -31887,7 +31922,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="172">
@@ -31934,7 +31969,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="173">
@@ -31981,7 +32016,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="174">
@@ -32028,7 +32063,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="175">
@@ -32075,7 +32110,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="176">
@@ -32122,7 +32157,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="177">
@@ -32169,7 +32204,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="178">
@@ -32216,7 +32251,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="179">
@@ -32263,7 +32298,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="180">
@@ -32310,7 +32345,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="181">
@@ -32357,7 +32392,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="182">
@@ -32404,7 +32439,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="183">
@@ -32451,7 +32486,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="184">
@@ -32498,7 +32533,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="185">
@@ -32545,7 +32580,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="186">
@@ -32592,7 +32627,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="187">
@@ -32639,7 +32674,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="188">
@@ -32686,7 +32721,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="189">
@@ -32733,7 +32768,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="190">
@@ -32780,7 +32815,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="191">
@@ -32827,7 +32862,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="192">
@@ -32874,7 +32909,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="193">
@@ -32921,7 +32956,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="194">
@@ -32968,7 +33003,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="195">
@@ -33015,7 +33050,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="196">
@@ -33062,7 +33097,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="197">
@@ -33109,7 +33144,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="198">
@@ -33156,7 +33191,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="199">
@@ -33203,7 +33238,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="200">
@@ -33250,7 +33285,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="201">
@@ -33297,7 +33332,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="202">
@@ -33344,7 +33379,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="203">
@@ -33391,7 +33426,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="204">
@@ -33438,7 +33473,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="205">
@@ -33485,7 +33520,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="206">
@@ -33532,7 +33567,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="207">
@@ -33579,7 +33614,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="208">
@@ -33626,7 +33661,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="209">
@@ -33673,7 +33708,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="210">
@@ -33720,7 +33755,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O210" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="211">
@@ -33767,7 +33802,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O211" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="212">
@@ -33814,7 +33849,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O212" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="213">
@@ -33861,7 +33896,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O213" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="214">
@@ -33908,7 +33943,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O214" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="215">
@@ -33955,7 +33990,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O215" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="216">
@@ -34002,7 +34037,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O216" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="217">
@@ -34049,7 +34084,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O217" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="218">
@@ -34096,7 +34131,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O218" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="219">
@@ -34143,7 +34178,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O219" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="220">
@@ -34190,7 +34225,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O220" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="221">
@@ -34237,7 +34272,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O221" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="222">
@@ -34284,7 +34319,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O222" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="223">
@@ -34331,7 +34366,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O223" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="224">
@@ -34378,7 +34413,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O224" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="225">
@@ -34425,7 +34460,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O225" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="226">
@@ -34472,7 +34507,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O226" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="227">
@@ -34519,7 +34554,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O227" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="228">
@@ -34566,7 +34601,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O228" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="229">
@@ -34613,7 +34648,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O229" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="230">
@@ -34660,7 +34695,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O230" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="231">
@@ -34707,7 +34742,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O231" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="232">
@@ -34754,7 +34789,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O232" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="233">
@@ -34801,7 +34836,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O233" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="234">
@@ -34848,7 +34883,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O234" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="235">
@@ -34895,7 +34930,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O235" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="236">
@@ -34942,7 +34977,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O236" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="237">
@@ -34989,7 +35024,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O237" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="238">
@@ -35036,7 +35071,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O238" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="239">
@@ -35083,7 +35118,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O239" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="240">
@@ -35130,7 +35165,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O240" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="241">
@@ -35177,7 +35212,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O241" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="242">
@@ -35224,7 +35259,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O242" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="243">
@@ -35271,7 +35306,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O243" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="244">
@@ -35318,7 +35353,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O244" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="245">
@@ -35365,7 +35400,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O245" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="246">
@@ -35412,7 +35447,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O246" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="247">
@@ -35459,7 +35494,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O247" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="248">
@@ -35506,7 +35541,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O248" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="249">
@@ -35553,7 +35588,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O249" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="250">
@@ -35600,7 +35635,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O250" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="251">
@@ -35647,7 +35682,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O251" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="252">
@@ -35694,7 +35729,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O252" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="253">
@@ -35741,7 +35776,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O253" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="254">
@@ -35788,7 +35823,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O254" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="255">
@@ -35835,7 +35870,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O255" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="256">
@@ -35882,7 +35917,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O256" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="257">
@@ -35929,7 +35964,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O257" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="258">
@@ -35976,7 +36011,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O258" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="259">
@@ -36023,7 +36058,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O259" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="260">
@@ -36070,7 +36105,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O260" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="261">
@@ -36117,7 +36152,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O261" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="262">
@@ -36164,7 +36199,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O262" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="263">
@@ -36211,7 +36246,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O263" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="264">
@@ -36258,7 +36293,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O264" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="265">
@@ -36305,7 +36340,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O265" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="266">
@@ -36352,7 +36387,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O266" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="267">
@@ -36399,7 +36434,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O267" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="268">
@@ -36446,7 +36481,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O268" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="269">
@@ -36493,7 +36528,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O269" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="270">
@@ -36540,7 +36575,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O270" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="271">
@@ -36587,7 +36622,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O271" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="272">
@@ -36634,7 +36669,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O272" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="273">
@@ -36681,7 +36716,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O273" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="274">
@@ -36728,7 +36763,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O274" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="275">
@@ -36775,7 +36810,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O275" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="276">
@@ -36822,7 +36857,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O276" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="277">
@@ -36869,7 +36904,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O277" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="278">
@@ -36916,7 +36951,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O278" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="279">
@@ -36963,7 +36998,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O279" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="280">
@@ -37010,7 +37045,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O280" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="281">
@@ -37057,7 +37092,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O281" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="282">
@@ -37104,7 +37139,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O282" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="283">
@@ -37151,7 +37186,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O283" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="284">
@@ -37198,7 +37233,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O284" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="285">
@@ -37245,7 +37280,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O285" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="286">
@@ -37292,7 +37327,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O286" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="287">
@@ -37339,7 +37374,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O287" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="288">
@@ -37386,7 +37421,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O288" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="289">
@@ -37433,7 +37468,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O289" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="290">
@@ -37480,7 +37515,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O290" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="291">
@@ -37527,7 +37562,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O291" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="292">
@@ -37574,7 +37609,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O292" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="293">
@@ -37621,7 +37656,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O293" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="294">
@@ -37668,7 +37703,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O294" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="295">
@@ -37715,7 +37750,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O295" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="296">
@@ -37762,7 +37797,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O296" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="297">
@@ -37809,7 +37844,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O297" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="298">
@@ -37856,7 +37891,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O298" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="299">
@@ -37903,7 +37938,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O299" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="300">
@@ -37950,7 +37985,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O300" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="301">
@@ -37997,7 +38032,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O301" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="302">
@@ -38044,7 +38079,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O302" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="303">
@@ -38091,7 +38126,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O303" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="304">
@@ -38138,7 +38173,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O304" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="305">
@@ -38185,7 +38220,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O305" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="306">
@@ -38232,7 +38267,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O306" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="307">
@@ -38279,7 +38314,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O307" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="308">
@@ -38326,7 +38361,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O308" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="309">
@@ -38373,7 +38408,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O309" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="310">
@@ -38420,7 +38455,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O310" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="311">
@@ -38467,7 +38502,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O311" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="312">
@@ -38514,7 +38549,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O312" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="313">
@@ -38561,7 +38596,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O313" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="314">
@@ -38608,7 +38643,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O314" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="315">
@@ -38655,7 +38690,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O315" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="316">
@@ -38702,7 +38737,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O316" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="317">
@@ -38749,7 +38784,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O317" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="318">
@@ -38796,7 +38831,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O318" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="319">
@@ -38843,7 +38878,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O319" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="320">
@@ -38890,7 +38925,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O320" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="321">
@@ -38937,7 +38972,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O321" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="322">
@@ -38984,7 +39019,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O322" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="323">
@@ -39031,7 +39066,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O323" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="324">
@@ -39078,7 +39113,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O324" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="325">
@@ -39125,7 +39160,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O325" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="326">
@@ -39172,7 +39207,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O326" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="327">
@@ -39219,7 +39254,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O327" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="328">
@@ -39266,7 +39301,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O328" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="329">
@@ -39313,7 +39348,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O329" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="330">
@@ -39360,7 +39395,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O330" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="331">
@@ -39407,7 +39442,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O331" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="332">
@@ -39454,7 +39489,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O332" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="333">
@@ -39501,7 +39536,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O333" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="334">
@@ -39548,7 +39583,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O334" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="335">
@@ -39595,7 +39630,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O335" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="336">
@@ -39642,7 +39677,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O336" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="337">
@@ -39689,7 +39724,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O337" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="338">
@@ -39736,7 +39771,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O338" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="339">
@@ -39783,7 +39818,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O339" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="340">
@@ -39830,7 +39865,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O340" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="341">
@@ -39877,7 +39912,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O341" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="342">
@@ -39924,7 +39959,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O342" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="343">
@@ -39971,7 +40006,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O343" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="344">
@@ -40018,7 +40053,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O344" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="345">
@@ -40065,7 +40100,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O345" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="346">
@@ -40112,7 +40147,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O346" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="347">
@@ -40159,7 +40194,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O347" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="348">
@@ -40206,7 +40241,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O348" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="349">
@@ -40253,7 +40288,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O349" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="350">
@@ -40300,7 +40335,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O350" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="351">
@@ -40347,7 +40382,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O351" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="352">
@@ -40394,7 +40429,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O352" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="353">
@@ -40441,7 +40476,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O353" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="354">
@@ -40488,7 +40523,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O354" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="355">
@@ -40535,7 +40570,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O355" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="356">
@@ -40582,7 +40617,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O356" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="357">
@@ -40629,7 +40664,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O357" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="358">
@@ -40676,7 +40711,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O358" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="359">
@@ -40723,7 +40758,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O359" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="360">
@@ -40770,7 +40805,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O360" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="361">
@@ -40817,7 +40852,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O361" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="362">
@@ -40864,7 +40899,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O362" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="363">
@@ -40911,7 +40946,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O363" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="364">
@@ -40958,7 +40993,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O364" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="365">
@@ -41005,7 +41040,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O365" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="366">
@@ -41052,7 +41087,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O366" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="367">
@@ -41099,7 +41134,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O367" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="368">
@@ -41146,7 +41181,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O368" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="369">
@@ -41193,7 +41228,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O369" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="370">
@@ -41240,7 +41275,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O370" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="371">
@@ -41287,7 +41322,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O371" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="372">
@@ -41334,7 +41369,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O372" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="373">
@@ -41381,7 +41416,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O373" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="374">
@@ -41428,7 +41463,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O374" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="375">
@@ -41475,7 +41510,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O375" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="376">
@@ -41522,7 +41557,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O376" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="377">
@@ -41569,7 +41604,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O377" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="378">
@@ -41616,7 +41651,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O378" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="379">
@@ -41663,7 +41698,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O379" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="380">
@@ -41710,7 +41745,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O380" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="381">
@@ -41757,7 +41792,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O381" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="382">
@@ -41804,7 +41839,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O382" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="383">
@@ -41851,7 +41886,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O383" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="384">
@@ -41898,7 +41933,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O384" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="385">
@@ -41945,7 +41980,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O385" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="386">
@@ -41992,7 +42027,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O386" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="387">
@@ -42039,7 +42074,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O387" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="388">
@@ -42086,7 +42121,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O388" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="389">
@@ -42133,7 +42168,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O389" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="390">
@@ -42180,7 +42215,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O390" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="391">
@@ -42227,7 +42262,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O391" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="392">
@@ -42274,7 +42309,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O392" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="393">
@@ -42321,7 +42356,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O393" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="394">
@@ -42368,7 +42403,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O394" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="395">
@@ -42415,7 +42450,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O395" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="396">
@@ -42462,7 +42497,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O396" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="397">
@@ -42509,7 +42544,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O397" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="398">
@@ -42556,7 +42591,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O398" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="399">
@@ -42603,7 +42638,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O399" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="400">
@@ -42650,7 +42685,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O400" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="401">
@@ -42697,7 +42732,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O401" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="402">
@@ -42744,7 +42779,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O402" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="403">
@@ -42791,7 +42826,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O403" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="404">
@@ -42838,7 +42873,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O404" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="405">
@@ -42885,7 +42920,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O405" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="406">
@@ -42932,7 +42967,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O406" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="407">
@@ -42979,7 +43014,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O407" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="408">
@@ -43026,7 +43061,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O408" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="409">
@@ -43073,7 +43108,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O409" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="410">
@@ -43120,7 +43155,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O410" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="411">
@@ -43167,7 +43202,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O411" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="412">
@@ -43214,7 +43249,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O412" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="413">
@@ -43261,7 +43296,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O413" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="414">
@@ -43308,7 +43343,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O414" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="415">
@@ -43355,7 +43390,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O415" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="416">
@@ -43402,7 +43437,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O416" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="417">
@@ -43449,7 +43484,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O417" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="418">
@@ -43496,7 +43531,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O418" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="419">
@@ -43543,7 +43578,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O419" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="420">
@@ -43590,7 +43625,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O420" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="421">
@@ -43637,7 +43672,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O421" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="422">
@@ -43684,7 +43719,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O422" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="423">
@@ -43731,7 +43766,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O423" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="424">
@@ -43778,7 +43813,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O424" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="425">
@@ -43825,7 +43860,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O425" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="426">
@@ -43872,7 +43907,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O426" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="427">
@@ -43919,7 +43954,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O427" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="428">
@@ -43966,7 +44001,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O428" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="429">
@@ -44013,7 +44048,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O429" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="430">
@@ -44060,7 +44095,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O430" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="431">
@@ -44107,7 +44142,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O431" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="432">
@@ -44154,7 +44189,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O432" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="433">
@@ -44201,7 +44236,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O433" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="434">
@@ -44248,7 +44283,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O434" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="435">
@@ -44295,7 +44330,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O435" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="436">
@@ -44342,7 +44377,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O436" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="437">
@@ -44389,7 +44424,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O437" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="438">
@@ -44436,7 +44471,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O438" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="439">
@@ -44483,7 +44518,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O439" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="440">
@@ -44530,7 +44565,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O440" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="441">
@@ -44577,7 +44612,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O441" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="442">
@@ -44624,7 +44659,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O442" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="443">
@@ -44671,7 +44706,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O443" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="444">
@@ -44718,7 +44753,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O444" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="445">
@@ -44765,7 +44800,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O445" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="446">
@@ -44812,7 +44847,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O446" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="447">
@@ -44859,7 +44894,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O447" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="448">
@@ -44906,7 +44941,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O448" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="449">
@@ -44953,7 +44988,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O449" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="450">
@@ -45000,7 +45035,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O450" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="451">
@@ -45047,7 +45082,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O451" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="452">
@@ -45094,7 +45129,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O452" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="453">
@@ -45141,7 +45176,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O453" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="454">
@@ -45188,7 +45223,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O454" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="455">
@@ -45235,7 +45270,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O455" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="456">
@@ -45282,7 +45317,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O456" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="457">
@@ -45329,7 +45364,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O457" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="458">
@@ -45376,7 +45411,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O458" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="459">
@@ -45423,7 +45458,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O459" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="460">
@@ -45470,7 +45505,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O460" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="461">
@@ -45517,7 +45552,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O461" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="462">
@@ -45564,7 +45599,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O462" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="463">
@@ -45611,7 +45646,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O463" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="464">
@@ -45658,7 +45693,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O464" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="465">
@@ -45705,7 +45740,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O465" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="466">
@@ -45752,7 +45787,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O466" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="467">
@@ -45799,7 +45834,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O467" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="468">
@@ -45846,7 +45881,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O468" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="469">
@@ -45893,7 +45928,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O469" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="470">
@@ -45940,7 +45975,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O470" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="471">
@@ -45987,7 +46022,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O471" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="472">
@@ -46034,7 +46069,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O472" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="473">
@@ -46081,7 +46116,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O473" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="474">
@@ -46128,7 +46163,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O474" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="475">
@@ -46175,7 +46210,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O475" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="476">
@@ -46222,7 +46257,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O476" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="477">
@@ -46269,7 +46304,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O477" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="478">
@@ -46316,7 +46351,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O478" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="479">
@@ -46363,7 +46398,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O479" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="480">
@@ -46410,7 +46445,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O480" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="481">
@@ -46457,7 +46492,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O481" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="482">
@@ -46504,7 +46539,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O482" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="483">
@@ -46551,7 +46586,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O483" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="484">
@@ -46598,7 +46633,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O484" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="485">
@@ -46645,7 +46680,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O485" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="486">
@@ -46692,7 +46727,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O486" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="487">
@@ -46739,7 +46774,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O487" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="488">
@@ -46786,7 +46821,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O488" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="489">
@@ -46833,7 +46868,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O489" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="490">
@@ -46880,7 +46915,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O490" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="491">
@@ -46927,7 +46962,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O491" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="492">
@@ -46974,7 +47009,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O492" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="493">
@@ -47021,7 +47056,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O493" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="494">
@@ -47068,7 +47103,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O494" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="495">
@@ -47115,7 +47150,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O495" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="496">
@@ -47162,7 +47197,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O496" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="497">
@@ -47209,7 +47244,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O497" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="498">
@@ -47256,7 +47291,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O498" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="499">
@@ -47303,7 +47338,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O499" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="500">
@@ -47350,7 +47385,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O500" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="501">
@@ -47397,7 +47432,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O501" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="502">
@@ -47444,7 +47479,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O502" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="503">
@@ -47491,7 +47526,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O503" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="504">
@@ -47538,7 +47573,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O504" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="505">
@@ -47585,7 +47620,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O505" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="506">
@@ -47632,7 +47667,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O506" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="507">
@@ -47679,7 +47714,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O507" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="508">
@@ -47726,7 +47761,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O508" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="509">
@@ -47773,7 +47808,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O509" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="510">
@@ -47820,7 +47855,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O510" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="511">
@@ -47867,7 +47902,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O511" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="512">
@@ -47914,7 +47949,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O512" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="513">
@@ -47961,7 +47996,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O513" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="514">
@@ -48008,7 +48043,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O514" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="515">
@@ -48055,7 +48090,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O515" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="516">
@@ -48102,7 +48137,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O516" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="517">
@@ -48149,7 +48184,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O517" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="518">
@@ -48196,7 +48231,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O518" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="519">
@@ -48243,7 +48278,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O519" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="520">
@@ -48290,7 +48325,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O520" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="521">
@@ -48337,7 +48372,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O521" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="522">
@@ -48384,7 +48419,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O522" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="523">
@@ -48431,7 +48466,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O523" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="524">
@@ -48478,7 +48513,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O524" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="525">
@@ -48525,7 +48560,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O525" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="526">
@@ -48572,7 +48607,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O526" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="527">
@@ -48619,7 +48654,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O527" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="528">
@@ -48666,7 +48701,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O528" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
     <row r="529">
@@ -48713,7 +48748,7 @@
         <v>2026-06-14T22:51:52.995Z</v>
       </c>
       <c r="O529" t="str">
-        <v>2026-06-21T22:45:44.575Z</v>
+        <v>2026-06-22T14:02:11.532Z</v>
       </c>
     </row>
   </sheetData>
